--- a/文档/需求/20260917_本体Excel导入模板/本体模型填写模板_v2.xlsx
+++ b/文档/需求/20260917_本体Excel导入模板/本体模型填写模板_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对象" sheetId="1" r:id="R8a50900f5aec4ce1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性" sheetId="2" r:id="R846d88afa7044146"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则" sheetId="3" r:id="Ra5635a20a09e4d6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动作" sheetId="4" r:id="R7d10018a0e974df8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对象" sheetId="1" r:id="R356b79b1e6e8431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性" sheetId="2" r:id="R479b997e755540f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则" sheetId="3" r:id="R60ea6be73d5d4c34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动作" sheetId="4" r:id="Rb082af8105d64fc8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -302,6 +302,14 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="请从下拉列表选择" error="仅允许选择工作台已定义的类型。" sqref="C2:C1001">
+      <x:formula1>"文本,数值,是／否,时间,数组,结构体,时间序列"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="请从下拉列表选择" error="仅允许选择工作台已定义的类型。" sqref="D2:D1001">
+      <x:formula1>"文本,数值,是／否,时间"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>

--- a/文档/需求/20260917_本体Excel导入模板/本体模型填写模板_v2.xlsx
+++ b/文档/需求/20260917_本体Excel导入模板/本体模型填写模板_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对象" sheetId="1" r:id="R356b79b1e6e8431a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性" sheetId="2" r:id="R479b997e755540f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则" sheetId="3" r:id="R60ea6be73d5d4c34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动作" sheetId="4" r:id="Rb082af8105d64fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对象" sheetId="1" r:id="Rd368f46525224d92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性" sheetId="2" r:id="R294c9951844948f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则" sheetId="3" r:id="R8768f54d92994e9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动作" sheetId="4" r:id="Rf32d6d46a64b4f46"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -58,6 +58,18 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="1">
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA12622"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE8E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
@@ -282,6 +294,7 @@
     <x:col min="3" max="3" width="17.780000686645508" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="17.780000686645508" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="42.220001220703125" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" hidden="1" width="12" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -301,13 +314,40 @@
         <x:v>显示格式</x:v>
       </x:c>
     </x:row>
+    <x:row r="2">
+      <x:c r="C2"/>
+      <x:c r="G2"/>
+      <x:c r="H2" t="str">
+        <x:v>文本</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="H3" t="str">
+        <x:v>数值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="H4" t="str">
+        <x:v>是／否</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="H5" t="str">
+        <x:v>时间</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="D2:D1001">
+    <x:cfRule type="expression" dxfId="0" priority="1">
+      <x:formula>AND($C2&lt;&gt;"时间序列",$D2&lt;&gt;"")</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:dataValidations count="2">
     <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="请从下拉列表选择" error="仅允许选择工作台已定义的类型。" sqref="C2:C1001">
       <x:formula1>"文本,数值,是／否,时间,数组,结构体,时间序列"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="请从下拉列表选择" error="仅允许选择工作台已定义的类型。" sqref="D2:D1001">
-      <x:formula1>"文本,数值,是／否,时间"</x:formula1>
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="请选择适用的观测值类型" error="仅当数据类型为时间序列时可选择观测值类型；其他类型请留空。" sqref="D2:D1001">
+      <x:formula1>IF($C2="时间序列",$H$2:$H$5,$H$6)</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
